--- a/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ALIMERKA OVIEDO BALONCESTO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_ALIMERKA OVIEDO BALONCESTO.xlsx
@@ -565,13 +565,13 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.372999999999999</v>
+        <v>8.1038</v>
       </c>
       <c r="E2" t="n">
-        <v>9.2089</v>
+        <v>8.3888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1641999999999999</v>
+        <v>-0.285</v>
       </c>
       <c r="G2" t="n">
         <v>6.9111</v>
@@ -610,13 +610,13 @@
         <v>4.4054</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8493999999999999</v>
+        <v>-0.4198000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7419</v>
+        <v>-0.07820000000000005</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1075999999999999</v>
+        <v>-0.3414999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-0.37</v>
@@ -643,13 +643,13 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0662</v>
+        <v>7.5241</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2894</v>
+        <v>6.2907</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7767999999999999</v>
+        <v>1.2334</v>
       </c>
       <c r="G3" t="n">
         <v>7.9512</v>
@@ -688,13 +688,13 @@
         <v>4.4055</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.0347</v>
+        <v>-0.5769</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.325</v>
+        <v>-0.3236</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7098</v>
+        <v>-0.2533</v>
       </c>
       <c r="V3" t="n">
         <v>0.3699</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. LOBACO MUNOZ</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5.791499999999999</v>
+        <v>7.3329</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2948</v>
+        <v>2.2423</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4967</v>
+        <v>5.0906</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6852</v>
+        <v>2.5855</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5256</v>
+        <v>-1.8541</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1596000000000002</v>
+        <v>4.4395</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4158</v>
+        <v>2.6786</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2559</v>
+        <v>-0.8044000000000004</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8403</v>
+        <v>3.4829</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7306</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.7304</v>
+        <v>-1.0496</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9997</v>
+        <v>0.9565</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3041</v>
+        <v>4.4055</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.5244</v>
+        <v>-1.5419</v>
       </c>
       <c r="R4" t="n">
-        <v>6.8285</v>
+        <v>5.9474</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9423</v>
+        <v>-0.2175</v>
       </c>
       <c r="T4" t="n">
-        <v>0.17</v>
+        <v>0.1763</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1123</v>
+        <v>-0.3937999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7444</v>
+        <v>0.5595</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2333</v>
+        <v>0.9294</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4889</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>R. LOBACO MUNOZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>4.9726</v>
+        <v>5.466800000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>1.693</v>
+        <v>3.7729</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2796</v>
+        <v>1.6939</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8351</v>
+        <v>2.6852</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.5728</v>
+        <v>2.5256</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4077</v>
+        <v>0.1596000000000002</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4433</v>
+        <v>5.4158</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1642</v>
+        <v>6.2559</v>
       </c>
       <c r="L5" t="n">
-        <v>3.6074</v>
+        <v>-0.8403</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6082</v>
+        <v>-2.7306</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.4086</v>
+        <v>-3.7304</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8004</v>
+        <v>0.9997</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2203000000000001</v>
+        <v>3.3041</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.6257</v>
+        <v>-3.5244</v>
       </c>
       <c r="R5" t="n">
-        <v>4.8461</v>
+        <v>6.8285</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2963</v>
+        <v>-1.2669</v>
       </c>
       <c r="T5" t="n">
-        <v>3.0694</v>
+        <v>-0.3519</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2268</v>
+        <v>-0.9151</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3789</v>
+        <v>0.7444</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1939</v>
+        <v>2.2333</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.185</v>
+        <v>-1.4889</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4.3117</v>
+        <v>2.4833</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4848999999999999</v>
+        <v>-0.8205</v>
       </c>
       <c r="F6" t="n">
-        <v>3.8268</v>
+        <v>3.3037</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5855</v>
+        <v>1.8351</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8541</v>
+        <v>-2.5728</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4395</v>
+        <v>4.4077</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6786</v>
+        <v>3.4433</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8044000000000004</v>
+        <v>-0.1642</v>
       </c>
       <c r="L6" t="n">
-        <v>3.4829</v>
+        <v>3.6074</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-1.6082</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0496</v>
+        <v>-2.4086</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9565</v>
+        <v>0.8004</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4055</v>
+        <v>0.2203000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5419</v>
+        <v>-4.6257</v>
       </c>
       <c r="R6" t="n">
-        <v>5.9474</v>
+        <v>4.8461</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.2386</v>
+        <v>0.8069</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5811</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.6576</v>
+        <v>0.251</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5595</v>
+        <v>-0.3789</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9294</v>
+        <v>-0.1939</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.37</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.555</v>
+        <v>2.2512</v>
       </c>
       <c r="E7" t="n">
-        <v>2.198</v>
+        <v>1.4418</v>
       </c>
       <c r="F7" t="n">
-        <v>1.357</v>
+        <v>0.8094</v>
       </c>
       <c r="G7" t="n">
         <v>3.443</v>
@@ -1000,13 +1000,13 @@
         <v>1.9825</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4205</v>
+        <v>0.1168</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5013</v>
+        <v>-0.2547</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9192</v>
+        <v>0.3716</v>
       </c>
       <c r="V7" t="n">
         <v>1.1144</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8391999999999999</v>
+        <v>1.1673</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8391999999999999</v>
+        <v>-0.1173000000000005</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.2845</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8391999999999999</v>
+        <v>3.334</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2696</v>
+        <v>-1.4366</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5696</v>
+        <v>4.7706</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8391999999999999</v>
+        <v>6.6861</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2696</v>
+        <v>2.5357</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5696</v>
+        <v>4.1505</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-3.3523</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-3.9723</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1013</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-6.8285</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>7.9299</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-1.2196</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-1.0939</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.1258</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.0484</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-3.1673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8895</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.971</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0815</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2582</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0456</v>
+        <v>0.2696</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3038</v>
+        <v>0.5696</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0728</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4134</v>
+        <v>0.2696</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4862</v>
+        <v>0.5696</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8146</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3678</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1824</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4405</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3216</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7622</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0718</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5765</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4953</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4075</v>
+        <v>-0.2953</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7575</v>
+        <v>-2.6195</v>
       </c>
       <c r="F10" t="n">
-        <v>0.35</v>
+        <v>2.3242</v>
       </c>
       <c r="G10" t="n">
-        <v>3.334</v>
+        <v>-0.2582</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4366</v>
+        <v>0.0456</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7706</v>
+        <v>-0.3038</v>
       </c>
       <c r="J10" t="n">
-        <v>6.6861</v>
+        <v>-1.0728</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5357</v>
+        <v>0.4134</v>
       </c>
       <c r="L10" t="n">
-        <v>4.1505</v>
+        <v>-1.4862</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.3523</v>
+        <v>0.8146</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.9723</v>
+        <v>-0.3678</v>
       </c>
       <c r="O10" t="n">
-        <v>0.62</v>
+        <v>1.1824</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1013</v>
+        <v>0.4405</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.8285</v>
+        <v>-1.3216</v>
       </c>
       <c r="R10" t="n">
-        <v>7.9299</v>
+        <v>1.7622</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.7944</v>
+        <v>-0.4776</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.7341</v>
+        <v>-0.225</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0604</v>
+        <v>-0.2526</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0484</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.1673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.081</v>
+        <v>-2.8222</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4712</v>
+        <v>-2.8131</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6098000000000001</v>
+        <v>-0.009200000000000097</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1929</v>
@@ -1312,13 +1312,13 @@
         <v>1.7622</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9092000000000001</v>
+        <v>0.1679</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1917</v>
+        <v>0.8496</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2824</v>
+        <v>-0.6817</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2378</v>
@@ -1345,13 +1345,13 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5282</v>
+        <v>-4.3845</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.8559</v>
+        <v>-5.332600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3276</v>
+        <v>0.9483</v>
       </c>
       <c r="G12" t="n">
         <v>7.9821</v>
@@ -1390,13 +1390,13 @@
         <v>7.4893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8841</v>
+        <v>-0.7404000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.67</v>
+        <v>-1.1469</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7859</v>
+        <v>0.4065</v>
       </c>
       <c r="V12" t="n">
         <v>0.9295</v>
@@ -1423,13 +1423,13 @@
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>25.003</v>
+        <v>27.6666</v>
       </c>
       <c r="E13" t="n">
-        <v>10.9526</v>
+        <v>11.2727</v>
       </c>
       <c r="F13" t="n">
-        <v>14.0504</v>
+        <v>16.3938</v>
       </c>
       <c r="G13" t="n">
         <v>36.1153</v>
@@ -1438,7 +1438,7 @@
         <v>4.9557</v>
       </c>
       <c r="I13" t="n">
-        <v>31.15939999999999</v>
+        <v>31.1594</v>
       </c>
       <c r="J13" t="n">
         <v>51.18119999999999</v>
@@ -1447,7 +1447,7 @@
         <v>24.1193</v>
       </c>
       <c r="L13" t="n">
-        <v>27.06140000000001</v>
+        <v>27.0614</v>
       </c>
       <c r="M13" t="n">
         <v>-15.0664</v>
@@ -1468,13 +1468,13 @@
         <v>47.359</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.4905</v>
+        <v>-3.8271</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.2124</v>
+        <v>-1.8924</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.2783</v>
+        <v>-1.9347</v>
       </c>
       <c r="V13" t="n">
         <v>-1.3174</v>
